--- a/project-management/skills/pmo-pert-estimate/examples/scenario-6-pa-portal-integration/pert-estimate.xlsx
+++ b/project-management/skills/pmo-pert-estimate/examples/scenario-6-pa-portal-integration/pert-estimate.xlsx
@@ -4650,59 +4650,59 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Requirements not frozen by stakeholders in time</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Organizational</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>F0, F1</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="20">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="H3">
+      <c r="H3" s="20">
         <f>IF(G3&gt;=15,"CRITICAL",IF(G3&gt;=10,"HIGH",IF(G3&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="20" t="inlineStr">
         <is>
           <t>Use a written sign-off gate before F1 starts</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="20">
         <f>L3*500</f>
         <v/>
       </c>
@@ -4766,117 +4766,117 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>API contract instability with internal data owners</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>F1, F2</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="20">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="H5">
+      <c r="H5" s="20">
         <f>IF(G5&gt;=15,"CRITICAL",IF(G5&gt;=10,"HIGH",IF(G5&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>Lock API contracts at end of F1 with both data owners</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>TA</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="20">
         <f>L5*500</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Business logic complexity underestimated</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="20">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="H6">
+      <c r="H6" s="20">
         <f>IF(G6&gt;=15,"CRITICAL",IF(G6&gt;=10,"HIGH",IF(G6&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>Buffer included in pessimistic estimates of F2.1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="20">
         <f>L6*500</f>
         <v/>
       </c>
@@ -4940,117 +4940,117 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Payments integration security review extra round</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>F3, F4</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="20">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="H8">
+      <c r="H8" s="20">
         <f>IF(G8&gt;=15,"CRITICAL",IF(G8&gt;=10,"HIGH",IF(G8&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>Pre-review of payments flow in F1 with security team</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="20">
         <f>L8*500</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Security audit findings require code rework</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>F4, F5</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="20">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="H9">
+      <c r="H9" s="20">
         <f>IF(G9&gt;=15,"CRITICAL",IF(G9&gt;=10,"HIGH",IF(G9&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>Apply security checklist throughout F2 to reduce findings</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>TA</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="20">
         <f>L9*500</f>
         <v/>
       </c>
@@ -5114,117 +5114,117 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>UAT defect rate exceeds expectations</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>F6</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="20">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="H11">
+      <c r="H11" s="20">
         <f>IF(G11&gt;=15,"CRITICAL",IF(G11&gt;=10,"HIGH",IF(G11&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>Pre-UAT walkthrough with the client before window opens</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="20">
         <f>L11*500</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Production deploy fails the release window</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>F7</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="20">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="H12">
+      <c r="H12" s="20">
         <f>IF(G12&gt;=15,"CRITICAL",IF(G12&gt;=10,"HIGH",IF(G12&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>Run a full dry-run deployment in pre-prod 1 week earlier</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>DEVOPS</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="20">
         <f>L12*500</f>
         <v/>
       </c>
